--- a/InFiRA-QA/301080-QA.xlsx
+++ b/InFiRA-QA/301080-QA.xlsx
@@ -1056,7 +1056,7 @@
         <v>55</v>
       </c>
       <c r="B36" s="6">
-        <v>249.3</v>
+        <v>248.3</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
